--- a/public/SOA_DMR_Monthly_Report.xlsx
+++ b/public/SOA_DMR_Monthly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboards Projects\Follow-Up Sheets Dashboard\follow-up-sheets-dashboard V3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BF5DDA-2037-439B-B73B-C33D9A7CC97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AECAE3-48A3-4335-82AB-008C51A94690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="GVMetadata" sheetId="3" state="veryHidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'May 2026'!$A$40:$T$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'May 2026'!$A$1:$Q$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'May 2026'!$A$40:$T$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'May 2026'!$A$1:$Q$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -384,7 +384,7 @@
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,19 +468,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1024,21 +1011,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1097,6 +1069,17 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1105,7 +1088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1120,58 +1103,28 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1184,144 +1137,171 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1370,82 +1350,46 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1844,7 +1788,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -1862,1051 +1806,1051 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="100.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="42"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="96" t="s">
+      <c r="A1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="47"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="60"/>
     </row>
     <row r="2" spans="1:17" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="49"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
     </row>
     <row r="3" spans="1:17" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="68"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="38"/>
     </row>
     <row r="4" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="36" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="32" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="51" t="s">
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="30"/>
+      <c r="Q4" s="71"/>
     </row>
     <row r="5" spans="1:17" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="70"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="31"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="72"/>
     </row>
     <row r="6" spans="1:17" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="50"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
     </row>
     <row r="7" spans="1:17" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="59"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="54"/>
     </row>
     <row r="8" spans="1:17" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="101" t="s">
+      <c r="C8" s="46"/>
+      <c r="D8" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="60" t="s">
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="62"/>
-      <c r="O8" s="60" t="s">
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="63"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="44"/>
     </row>
     <row r="9" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
     </row>
     <row r="10" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="105"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
     </row>
     <row r="12" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
     </row>
     <row r="13" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>5</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
     </row>
     <row r="14" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>6</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="105"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="22"/>
-      <c r="Q14" s="22"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
     </row>
     <row r="15" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>7</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
     </row>
     <row r="16" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>8</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
     </row>
     <row r="17" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>9</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="104" t="s">
+      <c r="C17" s="13"/>
+      <c r="D17" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="23" t="s">
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23" t="s">
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
     </row>
     <row r="18" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>10</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
     </row>
     <row r="19" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>11</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="105"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
-      <c r="Q19" s="22"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
     </row>
     <row r="20" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>12</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
     </row>
     <row r="21" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>13</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="22"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
     </row>
     <row r="22" spans="1:17" ht="137.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>14</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="105"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
     </row>
     <row r="23" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>15</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="105"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="105"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
     </row>
     <row r="24" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>16</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="105"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="105"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
     </row>
     <row r="25" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>17</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
     </row>
     <row r="26" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>18</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="104" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="23" t="s">
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23" t="s">
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
     </row>
     <row r="27" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>19</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="104" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="105"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="23" t="s">
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23" t="s">
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
     </row>
     <row r="28" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>20</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="105"/>
-      <c r="F28" s="105"/>
-      <c r="G28" s="105"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23" t="s">
+      <c r="C28" s="14"/>
+      <c r="D28" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
     </row>
     <row r="29" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>21</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="105"/>
-      <c r="F29" s="105"/>
-      <c r="G29" s="105"/>
-      <c r="H29" s="106"/>
-      <c r="I29" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="23"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
     </row>
     <row r="30" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>22</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="104" t="s">
+      <c r="C30" s="14"/>
+      <c r="D30" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E30" s="105"/>
-      <c r="F30" s="105"/>
-      <c r="G30" s="105"/>
-      <c r="H30" s="106"/>
-      <c r="I30" s="23" t="s">
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23" t="s">
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
     </row>
     <row r="31" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>23</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
     </row>
     <row r="32" spans="1:17" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>24</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="104" t="s">
+      <c r="C32" s="14"/>
+      <c r="D32" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="106"/>
-      <c r="I32" s="23" t="s">
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="23"/>
-      <c r="O32" s="23" t="s">
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="1:20" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>25</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="105"/>
-      <c r="F33" s="105"/>
-      <c r="G33" s="105"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="23"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
     </row>
     <row r="34" spans="1:20" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>26</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="105"/>
-      <c r="G34" s="105"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="23"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
     </row>
     <row r="35" spans="1:20" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>27</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="105"/>
-      <c r="F35" s="105"/>
-      <c r="G35" s="105"/>
-      <c r="H35" s="106"/>
-      <c r="I35" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J35" s="23"/>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
     </row>
     <row r="36" spans="1:20" ht="80.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>28</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="105"/>
-      <c r="F36" s="105"/>
-      <c r="G36" s="105"/>
-      <c r="H36" s="106"/>
-      <c r="I36" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
     </row>
     <row r="37" spans="1:20" s="1" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="25"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="27"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="17"/>
       <c r="R37"/>
       <c r="S37"/>
       <c r="T37"/>
     </row>
     <row r="38" spans="1:20" s="1" customFormat="1" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="108" t="s">
+      <c r="A38" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="107"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="29"/>
       <c r="R38"/>
       <c r="S38"/>
       <c r="T38"/>
     </row>
     <row r="39" spans="1:20" s="1" customFormat="1" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="76" t="s">
+      <c r="A39" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="90" t="s">
+      <c r="B39" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="55" t="s">
+      <c r="D39" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="71" t="s">
+      <c r="F39" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="72"/>
-      <c r="H39" s="71" t="s">
+      <c r="G39" s="23"/>
+      <c r="H39" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="I39" s="72"/>
-      <c r="J39" s="71" t="s">
+      <c r="I39" s="23"/>
+      <c r="J39" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="K39" s="72"/>
-      <c r="L39" s="28" t="s">
+      <c r="K39" s="23"/>
+      <c r="L39" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="M39" s="28" t="s">
+      <c r="M39" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="N39" s="28" t="s">
+      <c r="N39" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="O39" s="28" t="s">
+      <c r="O39" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="P39" s="73" t="s">
+      <c r="P39" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="Q39" s="28" t="s">
+      <c r="Q39" s="24" t="s">
         <v>10</v>
       </c>
       <c r="R39"/>
       <c r="S39"/>
       <c r="T39"/>
     </row>
-    <row r="40" spans="1:20" s="1" customFormat="1" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="77"/>
-      <c r="B40" s="91"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="28"/>
+    <row r="40" spans="1:20" s="1" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="76"/>
+      <c r="B40" s="92"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="24"/>
       <c r="F40" s="5" t="s">
         <v>20</v>
       </c>
@@ -2925,34 +2869,34 @@
       <c r="K40" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="29"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="25"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="25"/>
       <c r="R40"/>
       <c r="S40"/>
       <c r="T40"/>
     </row>
     <row r="41" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="95"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="15"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="12"/>
       <c r="R41"/>
       <c r="S41"/>
       <c r="T41"/>
@@ -2960,21 +2904,21 @@
     <row r="42" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="8"/>
-      <c r="C42" s="93"/>
+      <c r="C42" s="9"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
       <c r="N42" s="8"/>
       <c r="O42" s="8"/>
       <c r="P42" s="8"/>
-      <c r="Q42" s="18"/>
+      <c r="Q42" s="12"/>
       <c r="R42"/>
       <c r="S42"/>
       <c r="T42"/>
@@ -2982,21 +2926,21 @@
     <row r="43" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="8"/>
-      <c r="C43" s="93"/>
+      <c r="C43" s="9"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
       <c r="L43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="8"/>
       <c r="O43" s="8"/>
       <c r="P43" s="8"/>
-      <c r="Q43" s="18"/>
+      <c r="Q43" s="12"/>
       <c r="R43"/>
       <c r="S43"/>
       <c r="T43"/>
@@ -3004,21 +2948,21 @@
     <row r="44" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="8"/>
-      <c r="C44" s="93"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
       <c r="L44" s="8"/>
       <c r="M44" s="8"/>
       <c r="N44" s="8"/>
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
-      <c r="Q44" s="18"/>
+      <c r="Q44" s="12"/>
       <c r="R44"/>
       <c r="S44"/>
       <c r="T44"/>
@@ -3026,43 +2970,43 @@
     <row r="45" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="8"/>
-      <c r="C45" s="93"/>
+      <c r="C45" s="9"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
       <c r="N45" s="8"/>
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
-      <c r="Q45" s="18"/>
+      <c r="Q45" s="12"/>
       <c r="R45"/>
       <c r="S45"/>
       <c r="T45"/>
     </row>
-    <row r="46" spans="1:20" s="1" customFormat="1" ht="291" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="8"/>
-      <c r="C46" s="93"/>
+      <c r="C46" s="9"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
       <c r="N46" s="8"/>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
-      <c r="Q46" s="18"/>
+      <c r="Q46" s="12"/>
       <c r="R46"/>
       <c r="S46"/>
       <c r="T46"/>
@@ -3070,21 +3014,21 @@
     <row r="47" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
-      <c r="C47" s="93"/>
+      <c r="C47" s="9"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
       <c r="N47" s="8"/>
       <c r="O47" s="8"/>
       <c r="P47" s="8"/>
-      <c r="Q47" s="18"/>
+      <c r="Q47" s="12"/>
       <c r="R47"/>
       <c r="S47"/>
       <c r="T47"/>
@@ -3092,21 +3036,21 @@
     <row r="48" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
       <c r="B48" s="8"/>
-      <c r="C48" s="93"/>
+      <c r="C48" s="9"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
-      <c r="Q48" s="18"/>
+      <c r="Q48" s="12"/>
       <c r="R48"/>
       <c r="S48"/>
       <c r="T48"/>
@@ -3114,109 +3058,109 @@
     <row r="49" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
-      <c r="C49" s="93"/>
+      <c r="C49" s="9"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
       <c r="L49" s="8"/>
       <c r="M49" s="8"/>
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
       <c r="P49" s="8"/>
-      <c r="Q49" s="18"/>
+      <c r="Q49" s="12"/>
       <c r="R49"/>
       <c r="S49"/>
       <c r="T49"/>
     </row>
-    <row r="50" spans="1:20" s="1" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
-      <c r="C50" s="93"/>
+      <c r="C50" s="9"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
       <c r="P50" s="8"/>
-      <c r="Q50" s="18"/>
+      <c r="Q50" s="12"/>
       <c r="R50"/>
       <c r="S50"/>
       <c r="T50"/>
     </row>
-    <row r="51" spans="1:20" s="1" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
-      <c r="C51" s="93"/>
+      <c r="C51" s="9"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="17"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
       <c r="P51" s="8"/>
-      <c r="Q51" s="18"/>
+      <c r="Q51" s="12"/>
       <c r="R51"/>
       <c r="S51"/>
       <c r="T51"/>
     </row>
-    <row r="52" spans="1:20" s="1" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
-      <c r="C52" s="93"/>
+      <c r="C52" s="9"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
       <c r="P52" s="8"/>
-      <c r="Q52" s="18"/>
+      <c r="Q52" s="12"/>
       <c r="R52"/>
       <c r="S52"/>
       <c r="T52"/>
     </row>
-    <row r="53" spans="1:20" s="1" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20" s="1" customFormat="1" ht="291" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
-      <c r="C53" s="93"/>
+      <c r="C53" s="9"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
       <c r="P53" s="8"/>
-      <c r="Q53" s="18"/>
+      <c r="Q53" s="12"/>
       <c r="R53"/>
       <c r="S53"/>
       <c r="T53"/>
@@ -3224,21 +3168,21 @@
     <row r="54" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
-      <c r="C54" s="93"/>
+      <c r="C54" s="9"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="17"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
       <c r="P54" s="8"/>
-      <c r="Q54" s="18"/>
+      <c r="Q54" s="12"/>
       <c r="R54"/>
       <c r="S54"/>
       <c r="T54"/>
@@ -3246,149 +3190,173 @@
     <row r="55" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7"/>
       <c r="B55" s="8"/>
-      <c r="C55" s="93"/>
+      <c r="C55" s="9"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
       <c r="L55" s="8"/>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
-      <c r="Q55" s="18"/>
+      <c r="Q55" s="12"/>
       <c r="R55"/>
       <c r="S55"/>
       <c r="T55"/>
     </row>
-    <row r="56" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="10"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="94"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="19"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-      <c r="Q56" s="21"/>
+    <row r="56" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="12"/>
       <c r="R56"/>
       <c r="S56"/>
       <c r="T56"/>
     </row>
-    <row r="57" spans="1:20" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="109" t="s">
+    <row r="57" spans="1:20" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="7"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="12"/>
+      <c r="R57"/>
+      <c r="S57"/>
+      <c r="T57"/>
+    </row>
+    <row r="58" spans="1:20" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="B57" s="110"/>
-      <c r="C57" s="110"/>
-      <c r="D57" s="110"/>
-      <c r="E57" s="110"/>
-      <c r="F57" s="110"/>
-      <c r="G57" s="110"/>
-      <c r="H57" s="110"/>
-      <c r="I57" s="110"/>
-      <c r="J57" s="110"/>
-      <c r="K57" s="110"/>
-      <c r="L57" s="110"/>
-      <c r="M57" s="110"/>
-      <c r="N57" s="110"/>
-      <c r="O57" s="110"/>
-      <c r="P57" s="110"/>
-      <c r="Q57" s="111"/>
-    </row>
-    <row r="58" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="112" t="s">
+      <c r="B58" s="94"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
+      <c r="E58" s="94"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="94"/>
+      <c r="H58" s="94"/>
+      <c r="I58" s="94"/>
+      <c r="J58" s="94"/>
+      <c r="K58" s="94"/>
+      <c r="L58" s="94"/>
+      <c r="M58" s="94"/>
+      <c r="N58" s="94"/>
+      <c r="O58" s="94"/>
+      <c r="P58" s="94"/>
+      <c r="Q58" s="95"/>
+    </row>
+    <row r="59" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="B58" s="113"/>
-      <c r="C58" s="113"/>
-      <c r="D58" s="113"/>
-      <c r="E58" s="114"/>
-      <c r="F58" s="88" t="s">
+      <c r="B59" s="97"/>
+      <c r="C59" s="97"/>
+      <c r="D59" s="97"/>
+      <c r="E59" s="98"/>
+      <c r="F59" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="G58" s="88"/>
-      <c r="H58" s="88"/>
-      <c r="I58" s="88"/>
-      <c r="J58" s="88"/>
-      <c r="K58" s="88"/>
-      <c r="L58" s="88"/>
-      <c r="M58" s="88"/>
-      <c r="N58" s="88"/>
-      <c r="O58" s="88"/>
-      <c r="P58" s="88"/>
-      <c r="Q58" s="89"/>
-    </row>
-    <row r="59" spans="1:20" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="85" t="s">
+      <c r="G59" s="87"/>
+      <c r="H59" s="87"/>
+      <c r="I59" s="87"/>
+      <c r="J59" s="87"/>
+      <c r="K59" s="87"/>
+      <c r="L59" s="87"/>
+      <c r="M59" s="87"/>
+      <c r="N59" s="87"/>
+      <c r="O59" s="87"/>
+      <c r="P59" s="87"/>
+      <c r="Q59" s="88"/>
+    </row>
+    <row r="60" spans="1:20" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="B59" s="80"/>
-      <c r="C59" s="80"/>
-      <c r="D59" s="74" t="s">
+      <c r="B60" s="79"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E59" s="115"/>
-      <c r="F59" s="80" t="s">
+      <c r="E60" s="99"/>
+      <c r="F60" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="G59" s="80"/>
-      <c r="H59" s="80"/>
-      <c r="I59" s="80" t="s">
+      <c r="G60" s="79"/>
+      <c r="H60" s="79"/>
+      <c r="I60" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="J59" s="80"/>
-      <c r="K59" s="80"/>
-      <c r="L59" s="80"/>
-      <c r="M59" s="74" t="s">
+      <c r="J60" s="79"/>
+      <c r="K60" s="79"/>
+      <c r="L60" s="79"/>
+      <c r="M60" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="75"/>
-      <c r="O59" s="75"/>
-      <c r="P59" s="80" t="s">
+      <c r="N60" s="74"/>
+      <c r="O60" s="74"/>
+      <c r="P60" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="Q59" s="81"/>
-    </row>
-    <row r="60" spans="1:20" ht="156.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="86" t="s">
+      <c r="Q60" s="80"/>
+    </row>
+    <row r="61" spans="1:20" ht="156.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="79"/>
-      <c r="C60" s="87"/>
-      <c r="D60" s="84"/>
-      <c r="E60" s="84"/>
-      <c r="F60" s="82" t="s">
+      <c r="B61" s="78"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="G60" s="82"/>
-      <c r="H60" s="82"/>
-      <c r="I60" s="82"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
-      <c r="L60" s="82"/>
-      <c r="M60" s="78" t="s">
+      <c r="G61" s="81"/>
+      <c r="H61" s="81"/>
+      <c r="I61" s="81"/>
+      <c r="J61" s="81"/>
+      <c r="K61" s="81"/>
+      <c r="L61" s="81"/>
+      <c r="M61" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="N60" s="79"/>
-      <c r="O60" s="79"/>
-      <c r="P60" s="82"/>
-      <c r="Q60" s="83"/>
+      <c r="N61" s="78"/>
+      <c r="O61" s="78"/>
+      <c r="P61" s="81"/>
+      <c r="Q61" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="160">
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
@@ -3398,70 +3366,30 @@
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="I29:N29"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="I31:N31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="A38:Q38"/>
-    <mergeCell ref="M59:O59"/>
+    <mergeCell ref="M60:O60"/>
     <mergeCell ref="A39:A40"/>
-    <mergeCell ref="M60:O60"/>
-    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="M61:O61"/>
     <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:H61"/>
     <mergeCell ref="F60:H60"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A60:C60"/>
-    <mergeCell ref="F58:Q58"/>
-    <mergeCell ref="I59:L59"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="F59:Q59"/>
+    <mergeCell ref="I60:L60"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="B39:B40"/>
-    <mergeCell ref="I60:L60"/>
+    <mergeCell ref="I61:L61"/>
     <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A57:Q57"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="A58:Q58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="M39:M40"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A7:Q7"/>
@@ -3484,10 +3412,8 @@
     <mergeCell ref="I4:O5"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="I12:N12"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="I11:N11"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="I16:N16"/>
     <mergeCell ref="O16:Q16"/>
@@ -3496,6 +3422,23 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:Q24"/>
     <mergeCell ref="D4:H5"/>
     <mergeCell ref="I19:N19"/>
     <mergeCell ref="I20:N20"/>
@@ -3505,15 +3448,15 @@
     <mergeCell ref="O22:Q22"/>
     <mergeCell ref="O20:Q20"/>
     <mergeCell ref="I21:N21"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
     <mergeCell ref="H39:I39"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="L39:L40"/>
@@ -3524,11 +3467,19 @@
     <mergeCell ref="O26:Q26"/>
     <mergeCell ref="I27:N27"/>
     <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="I24:N24"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="I30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="I31:N31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="A38:Q38"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="I35:N35"/>
     <mergeCell ref="I36:N36"/>
     <mergeCell ref="A37:Q37"/>
     <mergeCell ref="O36:Q36"/>
@@ -3543,12 +3494,27 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="I29:N29"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="26" fitToHeight="0" orientation="landscape" verticalDpi="4294967295" r:id="rId1"/>
@@ -3559,27 +3525,9 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="22" max="17" man="1"/>
-    <brk id="42" max="17" man="1"/>
+    <brk id="49" max="17" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{40C1889B-4FB4-4B45-B274-25E20CF5522C}">
-          <x14:formula1>
-            <xm:f>'RCA and Action Taken'!$B$1:$B$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>P41:P56</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{76968B73-1B6C-4BDB-8C4A-6312601EA6DC}">
-          <x14:formula1>
-            <xm:f>'RCA and Action Taken'!$A$1:$A$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q41:Q56</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -3593,10 +3541,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>105</v>
       </c>
     </row>
